--- a/outputs/model_intersection_bidirectional/model_intersection_bidirectional_output.xlsx
+++ b/outputs/model_intersection_bidirectional/model_intersection_bidirectional_output.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bidirectional_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bidirectional_Granger" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intersection_Combination_Summar" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intersection_Combination_Detail" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossTable_Correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Bidirectional_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bidirectional_Granger" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Intersection_Combination_Summar" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Intersection_Combination_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CrossTable_Correlations" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,12 +589,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.7036896267922405</v>
+        <v>0.7663471634923666</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7505738788595241</v>
+        <v>0.7882030328586436</v>
       </c>
     </row>
     <row r="3">
@@ -635,12 +635,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9044841052648571</v>
+        <v>0.7759534505370373</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8147058823529412</v>
+        <v>0.7965518555127991</v>
       </c>
     </row>
     <row r="4">
@@ -681,12 +681,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5604513838048434</v>
+        <v>0.7655006264085082</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5637254901960785</v>
+        <v>0.7855533899880965</v>
       </c>
     </row>
     <row r="5">
@@ -727,12 +727,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-0.4627642563176874</v>
+        <v>0.7520742518702174</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4019607843137256</v>
+        <v>0.7702893919024691</v>
       </c>
     </row>
     <row r="6">
@@ -773,12 +773,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.1559845237116024</v>
+        <v>0.7526606674033228</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05485664719819713</v>
+        <v>0.7749586166631723</v>
       </c>
     </row>
     <row r="7">
@@ -819,12 +819,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>EU</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Silpo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.1367031092605868</v>
+        <v>0.7361112713493575</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3056858914728678</v>
+        <v>0.7549028432571119</v>
       </c>
     </row>
     <row r="8">
@@ -865,7 +865,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Вершки</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.1566232690763853</v>
+        <v>0.5739242968213558</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1221288515406163</v>
+        <v>0.3838240214529198</v>
       </c>
     </row>
     <row r="9">
@@ -911,7 +911,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Вершки</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-0.1932998328718862</v>
+        <v>0.3940856013980496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2198879551820729</v>
+        <v>0.18091277657875</v>
       </c>
     </row>
     <row r="10">
@@ -957,7 +957,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Вершки</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.1909864131780531</v>
+        <v>0.2785699917966109</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1607843137254902</v>
+        <v>0.04078729068912863</v>
       </c>
     </row>
     <row r="11">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1013,11 +1013,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Йогурт</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.1785008270119316</v>
+        <v>0.3989371973532387</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3687593134659932</v>
+        <v>0.01498279034557275</v>
       </c>
     </row>
     <row r="12">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1059,11 +1059,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Йогурт</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.06330319429279573</v>
+        <v>0.2152215520139093</v>
       </c>
       <c r="J12" t="n">
-        <v>0.26996299142885</v>
+        <v>-0.1451710902402117</v>
       </c>
     </row>
     <row r="13">
@@ -1105,11 +1105,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Масло вершкове</t>
+          <t>Інше/невідомо</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-0.06635777043711011</v>
+        <v>0.1737106273583781</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.03669467787114846</v>
+        <v>-0.141931568003331</v>
       </c>
     </row>
     <row r="14">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Масло вершкове</t>
+          <t>Вершки</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-0.09762200874519522</v>
+        <v>-0.2718251060802168</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.03109243697478992</v>
+        <v>-0.1669467787114846</v>
       </c>
     </row>
     <row r="15">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Масло вершкове</t>
+          <t>Вершки</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-0.1287376422864664</v>
+        <v>-0.366371762868381</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1352941176470588</v>
+        <v>-0.2588235294117647</v>
       </c>
     </row>
     <row r="16">
@@ -1233,21 +1233,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Вершки</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2992425531975654</v>
+        <v>-0.3259098310301362</v>
       </c>
       <c r="J16" t="n">
-        <v>0.30605849598441</v>
+        <v>-0.1997198879551821</v>
       </c>
     </row>
     <row r="17">
@@ -1279,25 +1279,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Вершки</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3115895090415932</v>
+        <v>0.1884104892122742</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3193871706315173</v>
+        <v>0.2051948051948052</v>
       </c>
     </row>
     <row r="18">
@@ -1325,25 +1325,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Йогурт</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3030069308570693</v>
+        <v>0.2499770612172288</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3234376391884689</v>
+        <v>0.1847980319240387</v>
       </c>
     </row>
     <row r="19">
@@ -1371,25 +1371,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Йогурт</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2933645038909488</v>
+        <v>0.1075825140492701</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3210413422447873</v>
+        <v>0.1850521878605922</v>
       </c>
     </row>
     <row r="20">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2996214605370722</v>
+        <v>0.7126675585790723</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3168991229186054</v>
+        <v>0.7491931841552139</v>
       </c>
     </row>
     <row r="21">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.286851015094869</v>
+        <v>0.7243015793768569</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3090518497776876</v>
+        <v>0.7651581201466009</v>
       </c>
     </row>
     <row r="22">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3073197788779528</v>
+        <v>0.7143242699340827</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4116781373872708</v>
+        <v>0.7540994549383854</v>
       </c>
     </row>
     <row r="23">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3196867460688807</v>
+        <v>0.7062219973746887</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4229630147407866</v>
+        <v>0.7448700019385678</v>
       </c>
     </row>
     <row r="24">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1615,11 +1615,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2841908338931914</v>
+        <v>0.7000585928250894</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3889124862365033</v>
+        <v>0.7379479170026346</v>
       </c>
     </row>
     <row r="25">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2514548301665495</v>
+        <v>0.6919138481746998</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3539858229094981</v>
+        <v>0.728943709404495</v>
       </c>
     </row>
     <row r="26">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2777858248126248</v>
+        <v>0.2141342211853096</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3819521583233612</v>
+        <v>0.228024455376302</v>
       </c>
     </row>
     <row r="27">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2460600593563748</v>
+        <v>0.3825223592438875</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3507090238460923</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="28">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.194237213355106</v>
+        <v>0.2320314661701811</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3631779984721161</v>
+        <v>0.1467262898017705</v>
       </c>
     </row>
     <row r="29">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-0.1551061682432662</v>
+        <v>-0.3711738463579771</v>
       </c>
       <c r="J29" t="n">
-        <v>0.07379679144385026</v>
+        <v>-0.4125054277029961</v>
       </c>
     </row>
     <row r="30">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>-0.2949693622721972</v>
+        <v>-0.2954618132239056</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2376336898395722</v>
+        <v>-0.3716891011723839</v>
       </c>
     </row>
     <row r="31">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7126675585790723</v>
+        <v>-0.5049290712381667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7491931841552139</v>
+        <v>-0.441923577941815</v>
       </c>
     </row>
     <row r="32">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7243015793768569</v>
+        <v>0.1836525316040573</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7651581201466009</v>
+        <v>0.03308270676691729</v>
       </c>
     </row>
     <row r="33">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7143242699340827</v>
+        <v>0.6144693949247175</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7540994549383854</v>
+        <v>0.3804511278195489</v>
       </c>
     </row>
     <row r="34">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2075,11 +2075,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7062219973746887</v>
+        <v>0.08873665636781734</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7448700019385678</v>
+        <v>0.1689075630252101</v>
       </c>
     </row>
     <row r="35">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7000585928250894</v>
+        <v>-0.4256996306263767</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7379479170026346</v>
+        <v>-0.4663865546218487</v>
       </c>
     </row>
     <row r="36">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6919138481746998</v>
+        <v>-0.4391686214545747</v>
       </c>
       <c r="J36" t="n">
-        <v>0.728943709404495</v>
+        <v>-0.3907563025210084</v>
       </c>
     </row>
     <row r="37">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.1857292721505089</v>
+        <v>0.7431085665278738</v>
       </c>
       <c r="J37" t="n">
-        <v>0.154746554766564</v>
+        <v>0.7542992814677459</v>
       </c>
     </row>
     <row r="38">
@@ -2250,20 +2250,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3326568050755541</v>
+        <v>0.7524084495955645</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1272727272727273</v>
+        <v>0.7657462867262077</v>
       </c>
     </row>
     <row r="39">
@@ -2296,20 +2296,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2699956200960648</v>
+        <v>0.7439098255882197</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1071918320512804</v>
+        <v>0.7540046033180415</v>
       </c>
     </row>
     <row r="40">
@@ -2342,20 +2342,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-0.1561672023154664</v>
+        <v>0.7423661201368158</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1404689535388624</v>
+        <v>0.7514248357997699</v>
       </c>
     </row>
     <row r="41">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-0.08031075216965339</v>
+        <v>0.7298728754787885</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1715154146765089</v>
+        <v>0.7373669358577026</v>
       </c>
     </row>
     <row r="42">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>-0.2924851312043633</v>
+        <v>0.7285579502597065</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2749674337820235</v>
+        <v>0.7336837486016382</v>
       </c>
     </row>
     <row r="43">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.1730870423925318</v>
+        <v>-0.160507460344506</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1703081232492997</v>
+        <v>-0.1794195254374928</v>
       </c>
     </row>
     <row r="44">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-0.3013088519893242</v>
+        <v>-0.00660672409130028</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3196078431372549</v>
+        <v>-0.06913421435635685</v>
       </c>
     </row>
     <row r="45">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Молоко питне</t>
+          <t>Сир твердий</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>-0.3191296370850484</v>
+        <v>0.1246362106791278</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2778711484593838</v>
+        <v>0.1911207051296744</v>
       </c>
     </row>
     <row r="46">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7431085665278738</v>
+        <v>0.007733775877491254</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7542992814677459</v>
+        <v>0.08944854537559706</v>
       </c>
     </row>
     <row r="47">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2673,11 +2673,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7524084495955645</v>
+        <v>-0.04711390966769936</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7657462867262077</v>
+        <v>-0.08727746417716022</v>
       </c>
     </row>
     <row r="48">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2719,11 +2719,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7439098255882197</v>
+        <v>-0.328335673313297</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7540046033180415</v>
+        <v>-0.2212331741207121</v>
       </c>
     </row>
     <row r="49">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2765,11 +2765,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7423661201368158</v>
+        <v>-0.0754148041486781</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7514248357997699</v>
+        <v>-0.137209016929409</v>
       </c>
     </row>
     <row r="50">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7298728754787885</v>
+        <v>0.06020775994164491</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7373669358577026</v>
+        <v>-0.04310875756309978</v>
       </c>
     </row>
     <row r="51">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7285579502597065</v>
+        <v>0.1641495966811906</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7336837486016382</v>
+        <v>0.1446401115343676</v>
       </c>
     </row>
     <row r="52">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-0.1790873357699617</v>
+        <v>-0.0465838482227809</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2113811514558391</v>
+        <v>0.007563025210084034</v>
       </c>
     </row>
     <row r="53">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>-0.04443468360383181</v>
+        <v>-0.02380625901568005</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.1264081593139869</v>
+        <v>-0.00196078431372549</v>
       </c>
     </row>
     <row r="54">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.06927903954982605</v>
+        <v>-0.1013016671090029</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1270030398242419</v>
+        <v>-0.09383753501400562</v>
       </c>
     </row>
     <row r="55">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>-0.01371556880129697</v>
+        <v>0.04827637321917223</v>
       </c>
       <c r="J55" t="n">
-        <v>0.08228397742075554</v>
+        <v>0.1669565217391304</v>
       </c>
     </row>
     <row r="56">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>-0.0581802457273296</v>
+        <v>-0.4926293986262085</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1425314806773773</v>
+        <v>-0.4811479219543951</v>
       </c>
     </row>
     <row r="57">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ConsumerUA</t>
+          <t>Novus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>-0.3810721442263271</v>
+        <v>0.2469334139611031</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2648719062092922</v>
+        <v>0.2700027506528238</v>
       </c>
     </row>
     <row r="58">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Сметана</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>-0.0802936107605772</v>
+        <v>-0.01911922946537279</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.134623946368088</v>
+        <v>-0.02521778839610745</v>
       </c>
     </row>
     <row r="59">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Сметана</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.00152579719352134</v>
+        <v>-0.1957957746022613</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.1397418815192715</v>
+        <v>-0.243296836743315</v>
       </c>
     </row>
     <row r="60">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>Silpo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Сметана</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3289,31 +3289,31 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.1107259095395241</v>
+        <v>-0.2963045782436428</v>
       </c>
       <c r="J60" t="n">
-        <v>0.08061069078075603</v>
+        <v>-0.2842685327341188</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Молоко питне</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3326,44 +3326,44 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.01503369762439692</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01764705882352941</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Молоко питне</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3381,35 +3381,35 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.04048352171520568</v>
+        <v>0.9995523375149811</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.01596638655462185</v>
+        <v>0.9994421090844146</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Сир твердий</t>
+          <t>Молоко питне</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3427,26 +3427,26 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>-0.1854789816535956</v>
+        <v>0.9995523375149811</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.2014005602240897</v>
+        <v>0.9994421090844146</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3464,35 +3464,35 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.1192418932716051</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2969801939913985</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3519,26 +3519,26 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>-0.4139767649030091</v>
+        <v>0.9996495010801055</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.3399945377871191</v>
+        <v>0.9995036962007005</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Novus</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3565,16 +3565,16 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2869793970579667</v>
+        <v>0.9996495010801055</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3418017764607077</v>
+        <v>0.9995036962007005</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3602,25 +3602,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>-0.02684293349305297</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.03048063119181684</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_real</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3657,16 +3657,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>-0.1978897299090629</v>
+        <v>0.9996747135047312</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.2636903525766888</v>
+        <v>0.9996120519123788</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>between_sources</t>
+          <t>within_variant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Silpo</t>
+          <t>ConsumerUA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>price_pchip</t>
+          <t>price_linear</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3703,423 +3703,9 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>-0.2982922421625523</v>
+        <v>0.9996747135047312</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.3156112407228596</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Молоко питне</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.9999999999999998</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Молоко питне</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>0.9995523375149811</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.9994421090844146</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Молоко питне</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>0.9995523375149811</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.9994421090844146</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Сир твердий</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Сир твердий</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0.9996495010801055</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.9995036962007005</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Сир твердий</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>0.9996495010801055</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.9995036962007005</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Сметана</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>0.9999999999999999</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Сметана</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>price_real</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>0.9996747135047312</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.9996120519123788</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>within_variant</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ConsumerUA</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Сметана</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>price_linear</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>price_pchip</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>0.9996747135047312</v>
-      </c>
-      <c r="J78" t="n">
         <v>0.9996120519123788</v>
       </c>
     </row>
